--- a/dist/credit_monthly_summary.xlsx
+++ b/dist/credit_monthly_summary.xlsx
@@ -11,8 +11,8 @@
     <sheet name="debit summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Credit Summary'!$A$2:$F$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'debit summary'!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Credit Summary'!$A$2:$AO$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'debit summary'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,10 +69,10 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:AO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -452,50 +452,295 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="A1" s="2" t="n"/>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CHASE #3444</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>BEGIN BALANCE</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>CASH / CHECK DEPOSIT</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>NO1 SUSHI 88 CORKBBO ACH</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>NYS DTF PIT TAX PAYMNT</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>KINDERCARE PORTLAND OR</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>AMAZON PRIME*ZH8618UZ3 AMZN.COM/BILL WA</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>IRS USATAXPYMT</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>CREDIT ONE BANK PAYMENT</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>PROG CASUALTY INS PREM</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>CITI CARD ONLINEPAYMENT</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>AMAZON.COMSEATTLEWA US</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*TN0 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*MZ5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*GE2 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*V25 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*ZA2 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*AU5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*BQ9 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>BILL PAY:NEW YORK STATE INS 237224 4BQ1P6KR</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>AMAZON.COM*N22FJSEATTLEWA US</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*YR6 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AD2" s="1" t="inlineStr">
+        <is>
+          <t>ARROW BANK NA WEB PMT</t>
+        </is>
+      </c>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>HUNTINGTON BANKSIL PAYMENT</t>
+        </is>
+      </c>
+      <c r="AF2" s="1" t="inlineStr">
+        <is>
+          <t>AMEX EPAYMENT ACH PMT</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
+          <t>BILL PAY:VEOLIA WATER NEW Y 200054 HBU1T6KR</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>BILL PAY:ASSOCIATED MUTUAL 210061 UBQ1P6KR</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="inlineStr">
+        <is>
+          <t>BILL PAY:ORANGE &amp; ROCKLAND 879293 5BQ1P6KR</t>
+        </is>
+      </c>
+      <c r="AJ2" s="1" t="inlineStr">
+        <is>
+          <t>PAYPAL INST XFER</t>
+        </is>
+      </c>
+      <c r="AK2" s="1" t="inlineStr">
+        <is>
+          <t>DISCOVER BANK NET/MOBILE</t>
+        </is>
+      </c>
+      <c r="AL2" s="1" t="inlineStr">
+        <is>
+          <t>434 / NYS COMMISSION</t>
+        </is>
+      </c>
+      <c r="AM2" s="1" t="inlineStr">
         <is>
           <t>TOTAL CREDIT</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="AN2" s="1" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="AO2" s="1" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
@@ -504,285 +749,775 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3">
-        <f>SUM(C3:C3)</f>
-        <v/>
-      </c>
-      <c r="E3" s="3">
-        <f>'debit summary'!B2</f>
-        <v/>
-      </c>
-      <c r="F3" s="3">
-        <f>B3+D3-E3</f>
+      <c r="D3" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1964.54</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>665</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>817.29</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>930.52</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2739.75</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>578</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>703</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AH3" s="3" t="n">
+        <v>723</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AJ3" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>833.8099999999999</v>
+      </c>
+      <c r="AL3" s="3" t="n">
+        <v>4589.17</v>
+      </c>
+      <c r="AM3" s="3">
+        <f>SUM(C3:AL3)</f>
+        <v/>
+      </c>
+      <c r="AN3" s="3">
+        <f>'debit summary'!B41</f>
+        <v/>
+      </c>
+      <c r="AO3" s="3">
+        <f>B3+AM3-AN3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
       <c r="B4" s="3">
-        <f>F3</f>
+        <f>AO3</f>
         <v/>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3">
-        <f>SUM(C4:C4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="3">
-        <f>'debit summary'!C2</f>
-        <v/>
-      </c>
-      <c r="F4" s="3">
-        <f>B4+D4-E4</f>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" s="3" t="n"/>
+      <c r="AF4" s="3" t="n"/>
+      <c r="AG4" s="3" t="n"/>
+      <c r="AH4" s="3" t="n"/>
+      <c r="AI4" s="3" t="n"/>
+      <c r="AJ4" s="3" t="n"/>
+      <c r="AK4" s="3" t="n"/>
+      <c r="AL4" s="3" t="n"/>
+      <c r="AM4" s="3">
+        <f>SUM(C4:AL4)</f>
+        <v/>
+      </c>
+      <c r="AN4" s="3">
+        <f>'debit summary'!C41</f>
+        <v/>
+      </c>
+      <c r="AO4" s="3">
+        <f>B4+AM4-AN4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
       <c r="B5" s="3">
-        <f>F4</f>
+        <f>AO4</f>
         <v/>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3">
-        <f>SUM(C5:C5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="3">
-        <f>'debit summary'!D2</f>
-        <v/>
-      </c>
-      <c r="F5" s="3">
-        <f>B5+D5-E5</f>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
+      <c r="AE5" s="3" t="n"/>
+      <c r="AF5" s="3" t="n"/>
+      <c r="AG5" s="3" t="n"/>
+      <c r="AH5" s="3" t="n"/>
+      <c r="AI5" s="3" t="n"/>
+      <c r="AJ5" s="3" t="n"/>
+      <c r="AK5" s="3" t="n"/>
+      <c r="AL5" s="3" t="n"/>
+      <c r="AM5" s="3">
+        <f>SUM(C5:AL5)</f>
+        <v/>
+      </c>
+      <c r="AN5" s="3">
+        <f>'debit summary'!D41</f>
+        <v/>
+      </c>
+      <c r="AO5" s="3">
+        <f>B5+AM5-AN5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>F5</f>
+        <f>AO5</f>
         <v/>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3">
-        <f>SUM(C6:C6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="3">
-        <f>'debit summary'!E2</f>
-        <v/>
-      </c>
-      <c r="F6" s="3">
-        <f>B6+D6-E6</f>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AE6" s="3" t="n"/>
+      <c r="AF6" s="3" t="n"/>
+      <c r="AG6" s="3" t="n"/>
+      <c r="AH6" s="3" t="n"/>
+      <c r="AI6" s="3" t="n"/>
+      <c r="AJ6" s="3" t="n"/>
+      <c r="AK6" s="3" t="n"/>
+      <c r="AL6" s="3" t="n"/>
+      <c r="AM6" s="3">
+        <f>SUM(C6:AL6)</f>
+        <v/>
+      </c>
+      <c r="AN6" s="3">
+        <f>'debit summary'!E41</f>
+        <v/>
+      </c>
+      <c r="AO6" s="3">
+        <f>B6+AM6-AN6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>F6</f>
+        <f>AO6</f>
         <v/>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3">
-        <f>SUM(C7:C7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="3">
-        <f>'debit summary'!F2</f>
-        <v/>
-      </c>
-      <c r="F7" s="3">
-        <f>B7+D7-E7</f>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" s="3" t="n"/>
+      <c r="X7" s="3" t="n"/>
+      <c r="Y7" s="3" t="n"/>
+      <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="3" t="n"/>
+      <c r="AE7" s="3" t="n"/>
+      <c r="AF7" s="3" t="n"/>
+      <c r="AG7" s="3" t="n"/>
+      <c r="AH7" s="3" t="n"/>
+      <c r="AI7" s="3" t="n"/>
+      <c r="AJ7" s="3" t="n"/>
+      <c r="AK7" s="3" t="n"/>
+      <c r="AL7" s="3" t="n"/>
+      <c r="AM7" s="3">
+        <f>SUM(C7:AL7)</f>
+        <v/>
+      </c>
+      <c r="AN7" s="3">
+        <f>'debit summary'!F41</f>
+        <v/>
+      </c>
+      <c r="AO7" s="3">
+        <f>B7+AM7-AN7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
       <c r="B8" s="3">
-        <f>F7</f>
+        <f>AO7</f>
         <v/>
       </c>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3">
-        <f>SUM(C8:C8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="3">
-        <f>'debit summary'!G2</f>
-        <v/>
-      </c>
-      <c r="F8" s="3">
-        <f>B8+D8-E8</f>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" s="3" t="n"/>
+      <c r="X8" s="3" t="n"/>
+      <c r="Y8" s="3" t="n"/>
+      <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AE8" s="3" t="n"/>
+      <c r="AF8" s="3" t="n"/>
+      <c r="AG8" s="3" t="n"/>
+      <c r="AH8" s="3" t="n"/>
+      <c r="AI8" s="3" t="n"/>
+      <c r="AJ8" s="3" t="n"/>
+      <c r="AK8" s="3" t="n"/>
+      <c r="AL8" s="3" t="n"/>
+      <c r="AM8" s="3">
+        <f>SUM(C8:AL8)</f>
+        <v/>
+      </c>
+      <c r="AN8" s="3">
+        <f>'debit summary'!G41</f>
+        <v/>
+      </c>
+      <c r="AO8" s="3">
+        <f>B8+AM8-AN8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <f>F8</f>
+        <f>AO8</f>
         <v/>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3">
-        <f>SUM(C9:C9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="3">
-        <f>'debit summary'!H2</f>
-        <v/>
-      </c>
-      <c r="F9" s="3">
-        <f>B9+D9-E9</f>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="n"/>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" s="3" t="n"/>
+      <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
+      <c r="AB9" s="3" t="n"/>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="3" t="n"/>
+      <c r="AE9" s="3" t="n"/>
+      <c r="AF9" s="3" t="n"/>
+      <c r="AG9" s="3" t="n"/>
+      <c r="AH9" s="3" t="n"/>
+      <c r="AI9" s="3" t="n"/>
+      <c r="AJ9" s="3" t="n"/>
+      <c r="AK9" s="3" t="n"/>
+      <c r="AL9" s="3" t="n"/>
+      <c r="AM9" s="3">
+        <f>SUM(C9:AL9)</f>
+        <v/>
+      </c>
+      <c r="AN9" s="3">
+        <f>'debit summary'!H41</f>
+        <v/>
+      </c>
+      <c r="AO9" s="3">
+        <f>B9+AM9-AN9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <f>F9</f>
+        <f>AO9</f>
         <v/>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3">
-        <f>SUM(C10:C10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="3">
-        <f>'debit summary'!I2</f>
-        <v/>
-      </c>
-      <c r="F10" s="3">
-        <f>B10+D10-E10</f>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="3" t="n"/>
+      <c r="X10" s="3" t="n"/>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="3" t="n"/>
+      <c r="AE10" s="3" t="n"/>
+      <c r="AF10" s="3" t="n"/>
+      <c r="AG10" s="3" t="n"/>
+      <c r="AH10" s="3" t="n"/>
+      <c r="AI10" s="3" t="n"/>
+      <c r="AJ10" s="3" t="n"/>
+      <c r="AK10" s="3" t="n"/>
+      <c r="AL10" s="3" t="n"/>
+      <c r="AM10" s="3">
+        <f>SUM(C10:AL10)</f>
+        <v/>
+      </c>
+      <c r="AN10" s="3">
+        <f>'debit summary'!I41</f>
+        <v/>
+      </c>
+      <c r="AO10" s="3">
+        <f>B10+AM10-AN10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <f>F10</f>
+        <f>AO10</f>
         <v/>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3">
-        <f>SUM(C11:C11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="3">
-        <f>'debit summary'!J2</f>
-        <v/>
-      </c>
-      <c r="F11" s="3">
-        <f>B11+D11-E11</f>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" s="3" t="n"/>
+      <c r="AF11" s="3" t="n"/>
+      <c r="AG11" s="3" t="n"/>
+      <c r="AH11" s="3" t="n"/>
+      <c r="AI11" s="3" t="n"/>
+      <c r="AJ11" s="3" t="n"/>
+      <c r="AK11" s="3" t="n"/>
+      <c r="AL11" s="3" t="n"/>
+      <c r="AM11" s="3">
+        <f>SUM(C11:AL11)</f>
+        <v/>
+      </c>
+      <c r="AN11" s="3">
+        <f>'debit summary'!J41</f>
+        <v/>
+      </c>
+      <c r="AO11" s="3">
+        <f>B11+AM11-AN11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <f>F11</f>
+        <f>AO11</f>
         <v/>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3">
-        <f>SUM(C12:C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="3">
-        <f>'debit summary'!K2</f>
-        <v/>
-      </c>
-      <c r="F12" s="3">
-        <f>B12+D12-E12</f>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
+      <c r="W12" s="3" t="n"/>
+      <c r="X12" s="3" t="n"/>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AE12" s="3" t="n"/>
+      <c r="AF12" s="3" t="n"/>
+      <c r="AG12" s="3" t="n"/>
+      <c r="AH12" s="3" t="n"/>
+      <c r="AI12" s="3" t="n"/>
+      <c r="AJ12" s="3" t="n"/>
+      <c r="AK12" s="3" t="n"/>
+      <c r="AL12" s="3" t="n"/>
+      <c r="AM12" s="3">
+        <f>SUM(C12:AL12)</f>
+        <v/>
+      </c>
+      <c r="AN12" s="3">
+        <f>'debit summary'!K41</f>
+        <v/>
+      </c>
+      <c r="AO12" s="3">
+        <f>B12+AM12-AN12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
       <c r="B13" s="3">
-        <f>F12</f>
+        <f>AO12</f>
         <v/>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3">
-        <f>SUM(C13:C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="3">
-        <f>'debit summary'!L2</f>
-        <v/>
-      </c>
-      <c r="F13" s="3">
-        <f>B13+D13-E13</f>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n"/>
+      <c r="X13" s="3" t="n"/>
+      <c r="Y13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="3" t="n"/>
+      <c r="AE13" s="3" t="n"/>
+      <c r="AF13" s="3" t="n"/>
+      <c r="AG13" s="3" t="n"/>
+      <c r="AH13" s="3" t="n"/>
+      <c r="AI13" s="3" t="n"/>
+      <c r="AJ13" s="3" t="n"/>
+      <c r="AK13" s="3" t="n"/>
+      <c r="AL13" s="3" t="n"/>
+      <c r="AM13" s="3">
+        <f>SUM(C13:AL13)</f>
+        <v/>
+      </c>
+      <c r="AN13" s="3">
+        <f>'debit summary'!L41</f>
+        <v/>
+      </c>
+      <c r="AO13" s="3">
+        <f>B13+AM13-AN13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
       <c r="B14" s="3">
-        <f>F13</f>
+        <f>AO13</f>
         <v/>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3">
-        <f>SUM(C14:C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="3">
-        <f>'debit summary'!M2</f>
-        <v/>
-      </c>
-      <c r="F14" s="3">
-        <f>B14+D14-E14</f>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
+      <c r="W14" s="3" t="n"/>
+      <c r="X14" s="3" t="n"/>
+      <c r="Y14" s="3" t="n"/>
+      <c r="Z14" s="3" t="n"/>
+      <c r="AA14" s="3" t="n"/>
+      <c r="AB14" s="3" t="n"/>
+      <c r="AC14" s="3" t="n"/>
+      <c r="AD14" s="3" t="n"/>
+      <c r="AE14" s="3" t="n"/>
+      <c r="AF14" s="3" t="n"/>
+      <c r="AG14" s="3" t="n"/>
+      <c r="AH14" s="3" t="n"/>
+      <c r="AI14" s="3" t="n"/>
+      <c r="AJ14" s="3" t="n"/>
+      <c r="AK14" s="3" t="n"/>
+      <c r="AL14" s="3" t="n"/>
+      <c r="AM14" s="3">
+        <f>SUM(C14:AL14)</f>
+        <v/>
+      </c>
+      <c r="AN14" s="3">
+        <f>'debit summary'!M41</f>
+        <v/>
+      </c>
+      <c r="AO14" s="3">
+        <f>B14+AM14-AN14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -797,16 +1532,156 @@
         <v/>
       </c>
       <c r="E15" s="3">
-        <f>'debit summary'!N2</f>
+        <f>SUM(E3:E14)</f>
         <v/>
       </c>
       <c r="F15" s="3">
-        <f>F14</f>
+        <f>SUM(F3:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="3">
+        <f>SUM(G3:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="3">
+        <f>SUM(H3:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="3">
+        <f>SUM(I3:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="3">
+        <f>SUM(J3:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(K3:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="3">
+        <f>SUM(L3:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>SUM(M3:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>SUM(N3:N14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="3">
+        <f>SUM(O3:O14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="3">
+        <f>SUM(P3:P14)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="3">
+        <f>SUM(Q3:Q14)</f>
+        <v/>
+      </c>
+      <c r="R15" s="3">
+        <f>SUM(R3:R14)</f>
+        <v/>
+      </c>
+      <c r="S15" s="3">
+        <f>SUM(S3:S14)</f>
+        <v/>
+      </c>
+      <c r="T15" s="3">
+        <f>SUM(T3:T14)</f>
+        <v/>
+      </c>
+      <c r="U15" s="3">
+        <f>SUM(U3:U14)</f>
+        <v/>
+      </c>
+      <c r="V15" s="3">
+        <f>SUM(V3:V14)</f>
+        <v/>
+      </c>
+      <c r="W15" s="3">
+        <f>SUM(W3:W14)</f>
+        <v/>
+      </c>
+      <c r="X15" s="3">
+        <f>SUM(X3:X14)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="3">
+        <f>SUM(Y3:Y14)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="3">
+        <f>SUM(Z3:Z14)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="3">
+        <f>SUM(AA3:AA14)</f>
+        <v/>
+      </c>
+      <c r="AB15" s="3">
+        <f>SUM(AB3:AB14)</f>
+        <v/>
+      </c>
+      <c r="AC15" s="3">
+        <f>SUM(AC3:AC14)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="3">
+        <f>SUM(AD3:AD14)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="3">
+        <f>SUM(AE3:AE14)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="3">
+        <f>SUM(AF3:AF14)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="3">
+        <f>SUM(AG3:AG14)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="3">
+        <f>SUM(AH3:AH14)</f>
+        <v/>
+      </c>
+      <c r="AI15" s="3">
+        <f>SUM(AI3:AI14)</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="3">
+        <f>SUM(AJ3:AJ14)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="3">
+        <f>SUM(AK3:AK14)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="3">
+        <f>SUM(AL3:AL14)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="3">
+        <f>SUM(AM3:AM14)</f>
+        <v/>
+      </c>
+      <c r="AN15" s="3">
+        <f>'debit summary'!N41</f>
+        <v/>
+      </c>
+      <c r="AO15" s="3">
+        <f>AO14</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F15"/>
+  <autoFilter ref="A2:AO15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -817,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -838,90 +1713,93 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>434 / Nys Commission</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
+      <c r="C2" s="3">
+        <f>4589.17</f>
+        <v/>
+      </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
@@ -932,11 +1810,1100 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="N2" s="3">
+        <f>SUM(B2:M2)</f>
+        <v/>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3">
+        <f>SUM(B3:M3)</f>
+        <v/>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon.Com*N22Fjseattlewa US</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3">
+        <f>109.43</f>
+        <v/>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3">
+        <f>SUM(B4:M4)</f>
+        <v/>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon.Comseattlewa US</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3">
+        <f>117.76</f>
+        <v/>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3">
+        <f>SUM(B5:M5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Amex Epayment ACH Pmt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3">
+        <f>1000.00</f>
+        <v/>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3">
+        <f>SUM(B6:M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Arrow Bank Na Web Pmt</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3">
+        <f>703.00</f>
+        <v/>
+      </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3">
+        <f>SUM(B7:M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3">
+        <f>723.00</f>
+        <v/>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3">
+        <f>SUM(B8:M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3">
+        <f>578.00</f>
+        <v/>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3">
+        <f>SUM(B9:M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3">
+        <f>SUM(B10:M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3">
+        <f>2400.00</f>
+        <v/>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3">
+        <f>SUM(B11:M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3">
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3">
+        <f>SUM(B12:M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3">
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3">
+        <f>SUM(B13:M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Citi Card Onlinepayment</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3">
+        <f>SUM(B14:M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Credit One Bank Payment</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3">
+        <f>SUM(B15:M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Discover Bank Net/Mobile</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3">
+        <f>833.81</f>
+        <v/>
+      </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3">
+        <f>SUM(B16:M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>18.58</f>
+        <v/>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3">
+        <f>SUM(B17:M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Huntington Banksil Payment</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3">
+        <f>900.00</f>
+        <v/>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3">
+        <f>SUM(B18:M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Internet Trf To Client-Added Transfer Account</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3">
+        <f>385.77+740.00+453.00+385.77</f>
+        <v/>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Irs Usataxpymt</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3">
+        <f>SUM(B20:M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Kindercare Portland OR</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3">
+        <f>490.00+120.00+55.00</f>
+        <v/>
+      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3">
+        <f>SUM(B21:M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3">
+        <f>4000.00+4000.00</f>
+        <v/>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3">
+        <f>SUM(B22:M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>413.63</f>
+        <v/>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3">
+        <f>SUM(B23:M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Nys Dtf Pit Tax Paymnt</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3">
+        <f>SUM(B24:M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>PANDA EXPRESS TACOMA WA</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <f>28.49</f>
+        <v/>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3">
+        <f>SUM(B25:M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Paypal Inst Xfer</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3">
+        <f>220.00</f>
+        <v/>
+      </c>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3">
+        <f>SUM(B26:M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3">
+        <f>SUM(B27:M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3">
+        <f>343.93</f>
+        <v/>
+      </c>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3">
+        <f>SUM(B28:M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3">
+        <f>17.59</f>
+        <v/>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3">
+        <f>SUM(B29:M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3">
+        <f>152.14</f>
+        <v/>
+      </c>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3">
+        <f>SUM(B30:M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3">
+        <f>71.79</f>
+        <v/>
+      </c>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3">
+        <f>SUM(B31:M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3">
+        <f>SUM(B32:M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3">
+        <f>SUM(B33:M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3">
+        <f>50.03</f>
+        <v/>
+      </c>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3">
+        <f>SUM(B34:M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3">
+        <f>20.80</f>
+        <v/>
+      </c>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3">
+        <f>SUM(B35:M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3">
+        <f>13.79</f>
+        <v/>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3">
+        <f>SUM(B36:M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3">
+        <f>40.33</f>
+        <v/>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3">
+        <f>SUM(B37:M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Prog Casualty Ins Prem</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3">
+        <f>SUM(B38:M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B39" s="3">
+        <f>95.44+101.98+76.47</f>
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3">
+        <f>SUM(B39:M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3">
+        <f>1000.00+3200.00+3800.00</f>
+        <v/>
+      </c>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3">
+        <f>SUM(B40:M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B41" s="3">
+        <f>SUM(B2:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="3">
+        <f>SUM(C2:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="3">
+        <f>SUM(D2:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(E2:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="3">
+        <f>SUM(F2:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="3">
+        <f>SUM(G2:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="3">
+        <f>SUM(H2:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="3">
+        <f>SUM(I2:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="3">
+        <f>SUM(J2:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="3">
+        <f>SUM(K2:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="3">
+        <f>SUM(L2:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="3">
+        <f>SUM(M2:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="3">
+        <f>SUM(B41:M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>